--- a/history_prices/MAR/prices_23032026.xlsx
+++ b/history_prices/MAR/prices_23032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD37A55-4610-4BBB-B083-6B1DBD843D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0F98BE-80AF-48ED-ADD4-0385DC85245E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
